--- a/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309930</t>
+          <t>309889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369793</t>
+          <t>369181</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1111308</t>
+          <t>1113082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1160960</t>
+          <t>1162558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1433646</t>
+          <t>1429752</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1525642</t>
+          <t>1522874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661930</t>
+          <t>662542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>721793</t>
+          <t>721834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153138</t>
+          <t>151540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202790</t>
+          <t>201016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>820179</t>
+          <t>822947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>912175</t>
+          <t>916069</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512281</t>
+          <t>511509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>588861</t>
+          <t>591173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1290322</t>
+          <t>1291712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1348543</t>
+          <t>1350094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1811184</t>
+          <t>1811924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1926172</t>
+          <t>1925930</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1103670</t>
+          <t>1101358</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1180250</t>
+          <t>1181022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236746</t>
+          <t>235195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294967</t>
+          <t>293577</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351648</t>
+          <t>1351890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1466636</t>
+          <t>1465896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207012</t>
+          <t>208493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255852</t>
+          <t>255506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>360796</t>
+          <t>358063</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>394431</t>
+          <t>394859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>577506</t>
+          <t>574507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>639066</t>
+          <t>637337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295556</t>
+          <t>295902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>344396</t>
+          <t>342915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80827</t>
+          <t>80399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114462</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>387600</t>
+          <t>389329</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>449160</t>
+          <t>452159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1063343</t>
+          <t>1064943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1174164</t>
+          <t>1177799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2789690</t>
+          <t>2791090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2877311</t>
+          <t>2877241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3881039</t>
+          <t>3878149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4032335</t>
+          <t>4043597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2101497</t>
+          <t>2097862</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2212318</t>
+          <t>2210718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497334</t>
+          <t>497404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584955</t>
+          <t>583555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2617972</t>
+          <t>2606710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2769268</t>
+          <t>2772158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>314745</t>
+          <t>313454</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376225</t>
+          <t>376906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1081348</t>
+          <t>1077830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1134717</t>
+          <t>1136388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1404872</t>
+          <t>1404288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1499336</t>
+          <t>1499819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597358</t>
+          <t>596677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>658838</t>
+          <t>660129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202080</t>
+          <t>200409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255449</t>
+          <t>258967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>811045</t>
+          <t>810562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>905509</t>
+          <t>906093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>839565</t>
+          <t>839665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>934144</t>
+          <t>932405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1457953</t>
+          <t>1458888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1521135</t>
+          <t>1519597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2307131</t>
+          <t>2318701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2435427</t>
+          <t>2436606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,49%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1029813</t>
+          <t>1031552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1124392</t>
+          <t>1124292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235666</t>
+          <t>237204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298848</t>
+          <t>297913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285331</t>
+          <t>1284152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1413627</t>
+          <t>1402057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237204</t>
+          <t>237148</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>284355</t>
+          <t>285614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>353011</t>
+          <t>353209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>388942</t>
+          <t>389248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>604358</t>
+          <t>603728</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>664545</t>
+          <t>663456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,59%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196826</t>
+          <t>195567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243977</t>
+          <t>244033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69689</t>
+          <t>69383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105620</t>
+          <t>105422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275268</t>
+          <t>276357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>335455</t>
+          <t>336085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1434711</t>
+          <t>1435290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1554783</t>
+          <t>1551396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2924690</t>
+          <t>2923481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3012314</t>
+          <t>3012822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4385784</t>
+          <t>4378619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4545139</t>
+          <t>4544182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1863939</t>
+          <t>1867326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1984011</t>
+          <t>1983432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539915</t>
+          <t>539407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>627539</t>
+          <t>628748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2425812</t>
+          <t>2426769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2585167</t>
+          <t>2592332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295692</t>
+          <t>291508</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>347699</t>
+          <t>345663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>817197</t>
+          <t>813681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>866650</t>
+          <t>865449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1116204</t>
+          <t>1121232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1198205</t>
+          <t>1201449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403958</t>
+          <t>405994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455965</t>
+          <t>460149</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125953</t>
+          <t>127154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175406</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>546055</t>
+          <t>542811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628056</t>
+          <t>623028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1067756</t>
+          <t>1065140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1159014</t>
+          <t>1157094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1736114</t>
+          <t>1739126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1792526</t>
+          <t>1793534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2820056</t>
+          <t>2820896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2936023</t>
+          <t>2937093</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>911992</t>
+          <t>913912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1003250</t>
+          <t>1005866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193799</t>
+          <t>192791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250211</t>
+          <t>247199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1121308</t>
+          <t>1120238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1237275</t>
+          <t>1236435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>338228</t>
+          <t>336259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>382439</t>
+          <t>382142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>454420</t>
+          <t>456784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>489060</t>
+          <t>488418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>802833</t>
+          <t>804142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>861853</t>
+          <t>861752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163475</t>
+          <t>163772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>207686</t>
+          <t>209655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59151</t>
+          <t>59793</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93791</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232272</t>
+          <t>232373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291292</t>
+          <t>289983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1731692</t>
+          <t>1731413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1848637</t>
+          <t>1850148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3039532</t>
+          <t>3038524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3119856</t>
+          <t>3122716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4795418</t>
+          <t>4794123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4949279</t>
+          <t>4949499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1519940</t>
+          <t>1518429</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1636885</t>
+          <t>1637164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>407283</t>
+          <t>404423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487607</t>
+          <t>488615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946437</t>
+          <t>1946217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2100298</t>
+          <t>2101593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266844</t>
+          <t>268785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308711</t>
+          <t>310912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>624677</t>
+          <t>625679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656181</t>
+          <t>656571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903045</t>
+          <t>903201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>954901</t>
+          <t>956313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,27%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206227</t>
+          <t>204026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248094</t>
+          <t>246153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99327</t>
+          <t>98937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130831</t>
+          <t>129829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315545</t>
+          <t>314133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>367401</t>
+          <t>367245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>959061</t>
+          <t>929677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1533206</t>
+          <t>1536495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2064642</t>
+          <t>2063978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2142768</t>
+          <t>2136282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2863376</t>
+          <t>2829615</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3686542</t>
+          <t>3702192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>756022</t>
+          <t>752733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1330167</t>
+          <t>1359551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93796</t>
+          <t>100282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171922</t>
+          <t>172586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>839250</t>
+          <t>823600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1662416</t>
+          <t>1696177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445741</t>
+          <t>445163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>494959</t>
+          <t>492993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>578951</t>
+          <t>578385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>612086</t>
+          <t>612140</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1035817</t>
+          <t>1034284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1098824</t>
+          <t>1096074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151664</t>
+          <t>153630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200882</t>
+          <t>201460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48377</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81512</t>
+          <t>82078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208262</t>
+          <t>211012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271269</t>
+          <t>272802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1664012</t>
+          <t>1604062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2299139</t>
+          <t>2294315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3293300</t>
+          <t>3296788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3396277</t>
+          <t>3393953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4762116</t>
+          <t>4807089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5697745</t>
+          <t>5688597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1151651</t>
+          <t>1156475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1786778</t>
+          <t>1846728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256258</t>
+          <t>258582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359235</t>
+          <t>355747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1405579</t>
+          <t>1414727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2341208</t>
+          <t>2296235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>309889</t>
+          <t>311641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369181</t>
+          <t>370987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1113082</t>
+          <t>1111445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1162558</t>
+          <t>1161041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1429752</t>
+          <t>1432270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1522874</t>
+          <t>1520434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662542</t>
+          <t>660736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>721834</t>
+          <t>720082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151540</t>
+          <t>153057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201016</t>
+          <t>202653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>822947</t>
+          <t>825387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>916069</t>
+          <t>913551</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>511509</t>
+          <t>512919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>591173</t>
+          <t>593314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1291712</t>
+          <t>1293522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1350094</t>
+          <t>1350243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1811924</t>
+          <t>1815993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1925930</t>
+          <t>1929927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1101358</t>
+          <t>1099217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1181022</t>
+          <t>1179612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235195</t>
+          <t>235046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>293577</t>
+          <t>291767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351890</t>
+          <t>1347893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1465896</t>
+          <t>1461827</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>208493</t>
+          <t>205534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255506</t>
+          <t>253667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>358063</t>
+          <t>360433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>394859</t>
+          <t>393750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>574507</t>
+          <t>573633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>637337</t>
+          <t>639476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295902</t>
+          <t>297741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342915</t>
+          <t>345874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80399</t>
+          <t>81508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117195</t>
+          <t>114825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389329</t>
+          <t>387190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452159</t>
+          <t>453033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1064943</t>
+          <t>1064692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1177799</t>
+          <t>1178098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2791090</t>
+          <t>2796494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2877241</t>
+          <t>2881418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3878149</t>
+          <t>3879112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4043597</t>
+          <t>4037308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2097862</t>
+          <t>2097563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2210718</t>
+          <t>2210969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497404</t>
+          <t>493227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583555</t>
+          <t>578151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2606710</t>
+          <t>2612999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2772158</t>
+          <t>2771195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313454</t>
+          <t>315439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>376906</t>
+          <t>376132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1077830</t>
+          <t>1079931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1136388</t>
+          <t>1137487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1404288</t>
+          <t>1401177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1499819</t>
+          <t>1497925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>596677</t>
+          <t>597451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>660129</t>
+          <t>658144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200409</t>
+          <t>199310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258967</t>
+          <t>256866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810562</t>
+          <t>812456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906093</t>
+          <t>909204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>839665</t>
+          <t>845272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>932405</t>
+          <t>933546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1458888</t>
+          <t>1455674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1519597</t>
+          <t>1519038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2318701</t>
+          <t>2316159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2436606</t>
+          <t>2433832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,41%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1031552</t>
+          <t>1030411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1124292</t>
+          <t>1118685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237204</t>
+          <t>237763</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297913</t>
+          <t>301127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284152</t>
+          <t>1286926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1402057</t>
+          <t>1404599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237148</t>
+          <t>235143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>285614</t>
+          <t>284420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>353209</t>
+          <t>355335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>389248</t>
+          <t>389958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>603728</t>
+          <t>606220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>663456</t>
+          <t>664265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195567</t>
+          <t>196761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244033</t>
+          <t>246038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69383</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105422</t>
+          <t>103296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276357</t>
+          <t>275548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>336085</t>
+          <t>333593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1435290</t>
+          <t>1433744</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1551396</t>
+          <t>1556234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2923481</t>
+          <t>2926020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3012822</t>
+          <t>3013354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4378619</t>
+          <t>4380828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4544182</t>
+          <t>4545543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1867326</t>
+          <t>1862488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1983432</t>
+          <t>1984978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539407</t>
+          <t>538875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628748</t>
+          <t>626209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2426769</t>
+          <t>2425408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2592332</t>
+          <t>2590123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291508</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345663</t>
+          <t>347475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>813681</t>
+          <t>818066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>865449</t>
+          <t>866945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1121232</t>
+          <t>1119803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1201449</t>
+          <t>1199005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>405994</t>
+          <t>404182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460149</t>
+          <t>458071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127154</t>
+          <t>125658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>174537</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>542811</t>
+          <t>545255</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>623028</t>
+          <t>624457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1065140</t>
+          <t>1064509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1157094</t>
+          <t>1157720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1739126</t>
+          <t>1737003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1793534</t>
+          <t>1794273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2820896</t>
+          <t>2813715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2937093</t>
+          <t>2927877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>913912</t>
+          <t>913286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005866</t>
+          <t>1006497</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192791</t>
+          <t>192052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>247199</t>
+          <t>249322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1120238</t>
+          <t>1129454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1236435</t>
+          <t>1243616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>336259</t>
+          <t>336448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>382142</t>
+          <t>382112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>456784</t>
+          <t>453874</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488418</t>
+          <t>488352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>804142</t>
+          <t>802824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>861752</t>
+          <t>861487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163772</t>
+          <t>163802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209655</t>
+          <t>209466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59793</t>
+          <t>59859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91427</t>
+          <t>94337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232373</t>
+          <t>232638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289983</t>
+          <t>291301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1731413</t>
+          <t>1735548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1850148</t>
+          <t>1849552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3038524</t>
+          <t>3037610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3122716</t>
+          <t>3120922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4794123</t>
+          <t>4791311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4949499</t>
+          <t>4941583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1518429</t>
+          <t>1519025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1637164</t>
+          <t>1633029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404423</t>
+          <t>406217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>488615</t>
+          <t>489529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1946217</t>
+          <t>1954133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2101593</t>
+          <t>2104405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>288546</t>
+          <t>325784</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>268785</t>
+          <t>302427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310912</t>
+          <t>348613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>641382</t>
+          <t>698660</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>625679</t>
+          <t>681969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>656571</t>
+          <t>714918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>929928</t>
+          <t>1024444</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903201</t>
+          <t>995278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>956313</t>
+          <t>1054637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>226392</t>
+          <t>252745</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>204026</t>
+          <t>229916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246153</t>
+          <t>276102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>123378</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>107120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129829</t>
+          <t>140069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>340518</t>
+          <t>376123</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>314133</t>
+          <t>345930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>367245</t>
+          <t>405289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1354415</t>
+          <t>1461796</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>929677</t>
+          <t>1405871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1536495</t>
+          <t>1509290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2101599</t>
+          <t>2017501</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2063978</t>
+          <t>1981361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2136282</t>
+          <t>2043463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3456014</t>
+          <t>3479297</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2829615</t>
+          <t>3414702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3702192</t>
+          <t>3538790</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>934813</t>
+          <t>767677</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>752733</t>
+          <t>720183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1359551</t>
+          <t>823602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>134965</t>
+          <t>152646</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100282</t>
+          <t>126684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172586</t>
+          <t>188786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1069778</t>
+          <t>920323</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>823600</t>
+          <t>860830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1696177</t>
+          <t>984918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289228</t>
+          <t>2229473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236564</t>
+          <t>2170147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525792</t>
+          <t>4399620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>470459</t>
+          <t>514603</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>445163</t>
+          <t>487830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>492993</t>
+          <t>540067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>597713</t>
+          <t>663039</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>578385</t>
+          <t>644181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>612140</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1068172</t>
+          <t>1177642</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1034284</t>
+          <t>1145388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1096074</t>
+          <t>1213431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>176164</t>
+          <t>196984</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153630</t>
+          <t>171520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201460</t>
+          <t>223757</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>71838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>57078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82078</t>
+          <t>90696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>268822</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>211012</t>
+          <t>233033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272802</t>
+          <t>301076</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2113420</t>
+          <t>2302183</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1604062</t>
+          <t>2239892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2294315</t>
+          <t>2364467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3340694</t>
+          <t>3379200</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3296788</t>
+          <t>3342360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3393953</t>
+          <t>3417286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5454113</t>
+          <t>5681383</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4807089</t>
+          <t>5603862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5688597</t>
+          <t>5759016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1337370</t>
+          <t>1217407</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1156475</t>
+          <t>1155123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1846728</t>
+          <t>1279698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>311841</t>
+          <t>347862</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258582</t>
+          <t>309776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355747</t>
+          <t>384702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1649211</t>
+          <t>1565269</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1414727</t>
+          <t>1487636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2296235</t>
+          <t>1642790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450790</t>
+          <t>3519590</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652535</t>
+          <t>3727062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7103324</t>
+          <t>7246652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
